--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486305_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486305_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.216799999999999</v>
+        <v>8.018599999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8009</v>
+        <v>6.6026</v>
       </c>
       <c r="F2" t="n">
         <v>1.416</v>
@@ -610,10 +610,10 @@
         <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2041</v>
+        <v>1.0058</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6682</v>
+        <v>0.4699</v>
       </c>
       <c r="U2" t="n">
         <v>0.536</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.228</v>
+        <v>5.5519</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6089</v>
+        <v>5.6244</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6191</v>
+        <v>-0.0725</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6678</v>
+        <v>4.6476</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2287</v>
+        <v>2.7495</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4391</v>
+        <v>1.8981</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6346</v>
+        <v>6.2853</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6456</v>
+        <v>3.0508</v>
       </c>
       <c r="L3" t="n">
-        <v>1.989</v>
+        <v>3.2345</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9668</v>
+        <v>-1.6377</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4169</v>
+        <v>-0.3013</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5499</v>
+        <v>-1.3364</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0175</v>
+        <v>0.4693</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1717</v>
+        <v>0.4266</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8459</v>
+        <v>0.0427</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4217</v>
+        <v>5.3987</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5559</v>
+        <v>5.1186</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1341</v>
+        <v>0.2801</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6476</v>
+        <v>1.6678</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7495</v>
+        <v>1.2287</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8981</v>
+        <v>0.4391</v>
       </c>
       <c r="J4" t="n">
-        <v>6.2853</v>
+        <v>3.6346</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0508</v>
+        <v>1.6456</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2345</v>
+        <v>1.989</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6377</v>
+        <v>-1.9668</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3013</v>
+        <v>-0.4169</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3364</v>
+        <v>-1.5499</v>
       </c>
       <c r="P4" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3391</v>
+        <v>1.1882</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3581</v>
+        <v>0.6814</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.019</v>
+        <v>0.5068</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9656</v>
+        <v>3.1035</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2796</v>
+        <v>3.5716</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.314</v>
+        <v>-0.4682</v>
       </c>
       <c r="G5" t="n">
         <v>1.0663</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3767</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4266</v>
+        <v>0.7186</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0499</v>
+        <v>-0.204</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.96</v>
+        <v>2.7059</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3656</v>
+        <v>1.1963</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5944</v>
+        <v>1.5096</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.1076</v>
+        <v>0.9821</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.3817</v>
+        <v>-0.1065</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2741</v>
+        <v>1.0885</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.2548</v>
+        <v>2.1663</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.4843</v>
+        <v>0.8244</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2295</v>
+        <v>1.342</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8528</v>
+        <v>-1.1843</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8974</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0446</v>
+        <v>-0.2534</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7401</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7626</v>
+        <v>0.3987</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2953</v>
+        <v>0.0973</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4673</v>
+        <v>0.3013</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.3252</v>
       </c>
       <c r="W6" t="n">
         <v>1.3252</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9234</v>
+        <v>1.4331</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3457</v>
+        <v>1.8554</v>
       </c>
       <c r="F7" t="n">
         <v>-0.4223</v>
@@ -1000,10 +1000,10 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4781</v>
+        <v>0.9878</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9421</v>
+        <v>0.4518</v>
       </c>
       <c r="U7" t="n">
         <v>0.536</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>C. VARELA ROMERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6325</v>
+        <v>1.3085</v>
       </c>
       <c r="E8" t="n">
-        <v>0.277</v>
+        <v>1.5233</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3555</v>
+        <v>-0.2148</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9821</v>
+        <v>1.7375</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1065</v>
+        <v>1.1861</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0885</v>
+        <v>0.5514</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1663</v>
+        <v>2.7743</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8244</v>
+        <v>1.2045</v>
       </c>
       <c r="L8" t="n">
-        <v>1.342</v>
+        <v>1.5698</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1843</v>
+        <v>-1.0368</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.0184</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2534</v>
+        <v>-1.0184</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3926</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3926</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6748</v>
+        <v>0.6585</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.822</v>
+        <v>0.9241</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1472</v>
+        <v>-0.2656</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. VARELA ROMERO</t>
+          <t>M. BRAZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7699</v>
+        <v>0.7685</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2313</v>
+        <v>1.0097</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4614</v>
+        <v>-0.2413</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7375</v>
+        <v>-0.3517</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1861</v>
+        <v>-0.3437</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5514</v>
+        <v>-0.008</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7743</v>
+        <v>0.6787</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2045</v>
+        <v>0.6022</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5698</v>
+        <v>0.0765</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0368</v>
+        <v>-1.0304</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0184</v>
+        <v>-0.9459</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0184</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1199</v>
+        <v>0.1631</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6321</v>
+        <v>0.3533</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5122</v>
+        <v>-0.1902</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. BRAZ</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3021</v>
+        <v>0.3051</v>
       </c>
       <c r="E10" t="n">
-        <v>0.451</v>
+        <v>0.0498</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1488</v>
+        <v>0.2553</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3517</v>
+        <v>-3.1076</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3437</v>
+        <v>-3.3817</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.008</v>
+        <v>0.2741</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6787</v>
+        <v>-2.2548</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6022</v>
+        <v>-2.4843</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0765</v>
+        <v>0.2295</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0304</v>
+        <v>-0.8528</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9459</v>
+        <v>-0.8974</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.0446</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3032</v>
+        <v>1.1077</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2055</v>
+        <v>0.9794</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0977</v>
+        <v>0.1283</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7395</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5443</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1094</v>
+        <v>-1.3713</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1802</v>
+        <v>-0.5962</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9292</v>
+        <v>-0.7751</v>
       </c>
       <c r="G11" t="n">
         <v>-4.4005</v>
@@ -1312,13 +1312,13 @@
         <v>2.3926</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2962</v>
+        <v>0.4419</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2139</v>
+        <v>0.3701</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0823</v>
+        <v>0.0718</v>
       </c>
       <c r="V11" t="n">
         <v>1.4997</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8985</v>
+        <v>-1.7828</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1793</v>
+        <v>-2.3718</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2807</v>
+        <v>0.589</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2276</v>
@@ -1390,13 +1390,13 @@
         <v>1.9576</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0635</v>
+        <v>0.0523</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5239</v>
+        <v>0.2836</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5396</v>
+        <v>-0.2313</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5649999999999999</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>24.4121</v>
+        <v>25.43969999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>22.5564</v>
+        <v>23.5837</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8559</v>
+        <v>1.8558</v>
       </c>
       <c r="G13" t="n">
-        <v>5.426899999999999</v>
+        <v>5.426900000000002</v>
       </c>
       <c r="H13" t="n">
         <v>3.315</v>
       </c>
       <c r="I13" t="n">
-        <v>2.111799999999999</v>
+        <v>2.111800000000001</v>
       </c>
       <c r="J13" t="n">
         <v>19.8594</v>
@@ -1459,7 +1459,7 @@
         <v>-6.781500000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>8.7003</v>
+        <v>8.700299999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-9.787699999999999</v>
@@ -1468,13 +1468,13 @@
         <v>18.4881</v>
       </c>
       <c r="S13" t="n">
-        <v>5.9603</v>
+        <v>6.987900000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>4.728800000000001</v>
+        <v>5.7561</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2317</v>
+        <v>1.2318</v>
       </c>
       <c r="V13" t="n">
         <v>4.3247</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7495</v>
+        <v>4.124</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6563</v>
+        <v>6.0975</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9068</v>
+        <v>-1.9735</v>
       </c>
       <c r="G14" t="n">
         <v>3.9598</v>
@@ -1546,13 +1546,13 @@
         <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2671</v>
+        <v>-0.3584</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4627</v>
+        <v>-0.0961</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1955</v>
+        <v>-0.2623</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5649999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4221</v>
+        <v>1.9629</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6305</v>
+        <v>1.9658</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2084</v>
+        <v>-0.0029</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5981</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7622</v>
+        <v>-0.2214</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.3377</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0893</v>
+        <v>0.1163</v>
       </c>
       <c r="V15" t="n">
         <v>1.695</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2005</v>
+        <v>-0.5201</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2353</v>
+        <v>1.453</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0348</v>
+        <v>-1.9732</v>
       </c>
       <c r="G16" t="n">
         <v>0.5323</v>
@@ -1702,13 +1702,13 @@
         <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5807</v>
+        <v>-0.14</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2846</v>
+        <v>0.5023</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.704</v>
+        <v>-0.6423</v>
       </c>
       <c r="V16" t="n">
         <v>-1.13</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6089</v>
+        <v>-1.1054</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7672</v>
+        <v>-0.3202</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8417</v>
+        <v>-0.7852</v>
       </c>
       <c r="G17" t="n">
         <v>-1.018</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6132</v>
+        <v>-0.1097</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3305</v>
+        <v>0.1166</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2828</v>
+        <v>-0.2262</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6127</v>
+        <v>-1.763</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4431</v>
+        <v>1.1078</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.0557</v>
+        <v>-2.8708</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5648</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5052</v>
+        <v>-0.6555</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0601</v>
+        <v>-0.2752</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5653</v>
+        <v>-0.3803</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1952</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.9285</v>
+        <v>-4.6177</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0638</v>
+        <v>-1.8403</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8647</v>
+        <v>-2.7774</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2332</v>
@@ -1936,13 +1936,13 @@
         <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7177</v>
+        <v>-0.4068</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3425</v>
+        <v>-0.119</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3752</v>
+        <v>-0.2878</v>
       </c>
       <c r="V19" t="n">
         <v>-1.3252</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.2337</v>
+        <v>-4.8625</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5179</v>
+        <v>-1.6296</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.7158</v>
+        <v>-3.2329</v>
       </c>
       <c r="G20" t="n">
         <v>1.023</v>
@@ -2014,13 +2014,13 @@
         <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9522</v>
+        <v>-0.581</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0036</v>
+        <v>-0.1081</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9558</v>
+        <v>-0.4729</v>
       </c>
       <c r="V20" t="n">
         <v>-3.5645</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.4353</v>
+        <v>-5.2118</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0483</v>
+        <v>-1.8247</v>
       </c>
       <c r="F21" t="n">
         <v>-3.3871</v>
@@ -2092,10 +2092,10 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0311</v>
+        <v>-0.8075</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.548</v>
+        <v>-0.3245</v>
       </c>
       <c r="U21" t="n">
         <v>-0.4831</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.7775</v>
+        <v>-5.2238</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5626</v>
+        <v>-3.0038</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2149</v>
+        <v>-2.22</v>
       </c>
       <c r="G22" t="n">
         <v>-0.638</v>
@@ -2170,13 +2170,13 @@
         <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1819</v>
+        <v>-0.6282</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9469</v>
+        <v>-0.3881</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2349</v>
+        <v>-0.2401</v>
       </c>
       <c r="V22" t="n">
         <v>-1.13</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.1877</v>
+        <v>-5.7047</v>
       </c>
       <c r="E23" t="n">
         <v>-3.8613</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3263</v>
+        <v>-1.8434</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5753</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0448</v>
+        <v>-0.5618</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2019</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8429</v>
+        <v>-0.3599</v>
       </c>
       <c r="V23" t="n">
         <v>0.5649999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-24.4122</v>
+        <v>-22.9221</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.855900000000001</v>
+        <v>-1.8558</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.5562</v>
+        <v>-21.0664</v>
       </c>
       <c r="G24" t="n">
         <v>-5.4269</v>
@@ -2326,13 +2326,13 @@
         <v>9.787499999999998</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.9605</v>
+        <v>-4.4703</v>
       </c>
       <c r="T24" t="n">
         <v>-1.2317</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.7288</v>
+        <v>-3.2386</v>
       </c>
       <c r="V24" t="n">
         <v>-4.3247</v>
